--- a/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица ЗПФ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\матрицы ПОКОМ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C54EE4-4BF4-4E7C-8929-5E6FCC2E709B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3288F9-9551-4FA5-A15A-0F3FD2022D5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="136">
   <si>
     <t>SU003945</t>
   </si>
@@ -435,20 +435,29 @@
     <t>Пельмени «Медвежье ушко Премиум со сливочным маслом» 0,4 классическая форма ТМ «Медвежье ушко»</t>
   </si>
   <si>
-    <t>P005438</t>
-  </si>
-  <si>
-    <t>P005439</t>
+    <t>SU004162</t>
+  </si>
+  <si>
+    <t>SU004163</t>
+  </si>
+  <si>
+    <t>новинка</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1570,23 +1579,36 @@
       </c>
       <c r="D64" s="3"/>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C65" t="s">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D65" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C66" t="s">
+      <c r="D65" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D66" t="s">
-        <v>134</v>
+      <c r="D66" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица ЗПФ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\матрицы ПОКОМ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3288F9-9551-4FA5-A15A-0F3FD2022D5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AE15EE-1F3D-40EF-82AF-E5BA8D1CE1DF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="142">
   <si>
     <t>SU003945</t>
   </si>
@@ -442,6 +442,24 @@
   </si>
   <si>
     <t>новинка</t>
+  </si>
+  <si>
+    <t>ВЫВОД</t>
+  </si>
+  <si>
+    <t>SU004310</t>
+  </si>
+  <si>
+    <t>Вареники «Медвежье ушко Премиум с картофелем и лесными грибами» 0,6 классическая форма ТМ «Медвежье ушко»</t>
+  </si>
+  <si>
+    <t>SU004023</t>
+  </si>
+  <si>
+    <t>Наггетсы «Сливушки в темпуре» Фикс.вес 0,23 ТМ «Вязанка»</t>
+  </si>
+  <si>
+    <t>ВВОД</t>
   </si>
 </sst>
 </file>
@@ -463,7 +481,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -473,6 +491,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -504,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -517,6 +547,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -797,12 +833,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="105" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="6" max="6" width="89.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1195,7 +1232,7 @@
       </c>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1207,7 +1244,7 @@
       </c>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1219,7 +1256,7 @@
       </c>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1231,7 +1268,7 @@
       </c>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1243,7 +1280,7 @@
       </c>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1255,7 +1292,7 @@
       </c>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1267,7 +1304,7 @@
       </c>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1279,7 +1316,7 @@
       </c>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -1291,7 +1328,7 @@
       </c>
       <c r="D40" s="3"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1303,7 +1340,7 @@
       </c>
       <c r="D41" s="3"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -1315,7 +1352,7 @@
       </c>
       <c r="D42" s="3"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -1327,7 +1364,7 @@
       </c>
       <c r="D43" s="3"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -1339,7 +1376,7 @@
       </c>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -1351,7 +1388,7 @@
       </c>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -1363,29 +1400,51 @@
       </c>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="D47" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D48" s="3"/>
+      <c r="D48" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">

--- a/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица ЗПФ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\матрицы ПОКОМ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AE15EE-1F3D-40EF-82AF-E5BA8D1CE1DF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE31B42F-1005-4779-A2BC-DE297CAF582C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="143">
   <si>
     <t>SU003945</t>
   </si>
@@ -460,6 +460,9 @@
   </si>
   <si>
     <t>ВВОД</t>
+  </si>
+  <si>
+    <t>вывел завод</t>
   </si>
 </sst>
 </file>
@@ -481,7 +484,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -503,6 +506,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -534,7 +543,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -553,6 +562,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1195,16 +1208,18 @@
       <c r="D29" s="3"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="A30" s="10">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="11" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4">

--- a/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица ЗПФ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\матрицы ПОКОМ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE31B42F-1005-4779-A2BC-DE297CAF582C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B40AE0-A1FC-4EEF-809F-849DF1FA92B3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
